--- a/aircraft/reports/top-airlines-over-time-yearly.xlsx
+++ b/aircraft/reports/top-airlines-over-time-yearly.xlsx
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68">

--- a/aircraft/reports/top-airlines-over-time-yearly.xlsx
+++ b/aircraft/reports/top-airlines-over-time-yearly.xlsx
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="65">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68">

--- a/aircraft/reports/top-airlines-over-time-yearly.xlsx
+++ b/aircraft/reports/top-airlines-over-time-yearly.xlsx
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66">
@@ -1482,12 +1482,12 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B67" t="n">
         <v>2025</v>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B68" t="n">
         <v>2025</v>
@@ -1514,12 +1514,12 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B69" t="n">
         <v>2025</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B70" t="n">
         <v>2025</v>
@@ -1546,12 +1546,12 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B71" t="n">
         <v>2025</v>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/top-airlines-over-time-yearly.xlsx
+++ b/aircraft/reports/top-airlines-over-time-yearly.xlsx
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="67">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="71">

--- a/aircraft/reports/top-airlines-over-time-yearly.xlsx
+++ b/aircraft/reports/top-airlines-over-time-yearly.xlsx
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="70">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="71">
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
